--- a/human_validation/judge/kor/judge_D013_S001_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S001_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제일 큰 문제는 잠인 것 같아요. 직원 지원 프로그램에 결국 전화한 건 요즘 잠을 거의 제대로 못 자서예요. 누워 있으면 일 문제랑 집에서 있었던 다툼들을 계속 되새기게 되고, 그러다 새벽 3~4시쯤 깨요. 하루를 시작할 때쯤이면 제대로 쉰 적이 없는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 일상적인 일들에 대해 지나치게 걱정하시는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 이것저것 생각을 하긴 하는데, 그게 지나친 걱정인지는 모르겠어요. 그냥 가끔 머릿속에 뭔가가 걸려서 안 빠지는 느낌에 더 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 낮 동안 피곤하거나 지친 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 그래요. 대부분의 날에는 꽤 지친 상태로, 이미 진 빠진 채로 하루를 시작하는 느낌이에요. 새벽 3~4시쯤 깨서 제대로 다시 잠들지 못하니까, 실제로 쉰 적이 없는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 최근에 공황 발작을 경험하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 갑자기 숨을 못 쉬겠다거나 통제력을 잃는 것 같은 느낌은 없었어요. 적어도 제가 공황 발작이라고 부를 만한 건 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 수면 부족 때문에 직장이나 집에서 집중하거나 초점을 맞추는 데 어려움을 겪고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 확실히요. 특히 직장에서요. 예전엔 영업 예측이나 고객 프레젠테이션을 꽤 빨리 끝냈는데, 지금은 같은 슬라이드를 계속 읽고, 숫자를 다시 의심하고, 그래도 뭘 말하려는 건지 계속 막혀 있는 느낌이에요. 답답해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 직장이나 집에서 수면 문제에 영향을 주고 있을 만한 특별히 스트레스 받는 일이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 주로 일 문제랑 집에서의 다툼들이에요. 침대에 누우면 하루를 되짚어보게 돼요 — 해야 할 일, 망친 일, 잘 안 풀렸던 대화들 같은 거요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유예요, 잠을 제대로 못 자니까요. 새벽 3~4시쯤 깨고 나면 하루가 제대로 쉰 적이 없는 느낌으로 시작돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 항상 같은 시간에 깨는 것처럼, 깨는 시간에 어떤 패턴이나 규칙성을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네, 꽤 규칙적이에요. 보통 새벽 3~4시쯤 깨고, 그냥 깨어 있으면서 일이나 집에서의 다툼에 대해 생각하게 돼요. 그러고 나면 한참 침대에 있었어도 실제로 쉬었다는 느낌이 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 반복되는 악몽이나 불쾌한 꿈을 꾸시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 악몽까지는 아니에요. 그보다는 계속 잠들어 있지를 못하는 거예요 — 누워서 일 문제나 집에서의 다툼을 계속 되새기다가, 새벽 3~4시쯤 깨서 그냥 제대로 쉰 적이 없는 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 한밤중에 깨기 직전에 특별히 생각하거나 걱정하는 게 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네, 보통은 일이거나 집에서 다투다가 제가 한 말 같은 거예요. 반쯤 깨어 있는 상태에서 이미 그걸 되새기고 있어요 — 뭘 망쳤는지, 앞으로 뭘 처리해야 하는지 — 그러다 새벽 3~4시쯤 완전히 깨요. 그 이후에는 잤다는 느낌이 별로 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 밤 초반에 잠드는 데 어려움을 겪으시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네, 어떤 날은 그래요. 침대에 누워서 그냥 일 문제나 집에서의 다툼을 계속 되새기게 돼요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유 중 하나예요 — 잠을 제대로 못 자고, 잠들어도 새벽 3~4시쯤 깨서 하루를 제대로 못 쉰 느낌으로 시작해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 잠들기 직전에 일어나는 일이나 생각하는 게 몇 시간 후에 깨는 것과 관련이 있을 만한 게 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네, 주로 누워서 일 문제나 집에서의 다툼을 되새기고 있는 것 같아요. 무슨 일이 있었는지, 뭘 처리해야 하는지 계속 되풀이하다가, 결국 새벽 3~4시쯤 깨게 돼요. 그게 정말 직원 지원 프로그램에 전화하게 만든 이유예요 — 그냥 잠을 제대로 못 자고, 전혀 쉰 적이 없는 느낌으로 하루를 시작해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 직장이나 집에서 특별히 가장 스트레스를 많이 주고 수면 문제에 영향을 주는 한 가지가 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 딱 한 가지는 아니에요, 정말로요. 업무 스트레스랑 집에서의 다툼이 합쳐진 거예요. 침대에 누워서 그걸 다 되새기기 시작하고, 잠이 들어도 새벽 3~4시쯤 깨요. 그게 결국 직원 지원 프로그램에 전화하게 만든 거예요 — 잠을 거의 못 자고 전혀 쉬지 못한 느낌으로 하루를 시작해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 침대에 누워서 잠을 못 잘 때 불안하거나 초조한 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 불안이라고 딱 말할 수 있을지는 모르겠어요. 확실히 긴장돼 있고 머릿속이 바쁘긴 한데, 그게 불안인지 아니면 그냥... 생각을 끌 수가 없는 건지 제대로 신경 써서 본 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 직장 스트레스나 집에서의 다툼이 항상 머릿속에 있나요, 아니면 그런 생각들을 잠시 밀어둘 수 있는 때도 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 낮에는 밀어둘 수 있는 시간이 있어요, 특히 바쁠 때는요. 근데 밤이 되면 다시 돌아와요. 침대에 누우면 일 문제나 집에서의 다툼을 다시 되새기게 되고, 그러다 새벽 3~4시쯤 깨서 제대로 잔 적이 없는 느낌이 들어요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 지금 상태 때문에 사회적 관계나 여가 활동에 어려움을 겪고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 네, 그런 것 같아요. 예전엔 픽업 농구, 볼링 나이트, 음악 페스티벌, 아니면 친구들 불러서 훈제기 돌리는 것 같은 걸 정말 기대했거든요. 요즘엔 취소하거나, 가더라도 그냥 거기 있기만 해요... 즐기기보다는 그냥 하는 척만 하는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 수면 문제가 시작된 것과 비슷한 시기에 시작된 특별한 일이 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 네. 집에서의 다툼이 훨씬 심해졌을 때 시작된 것 같아요. 그게... 이제 한 1년 2개월쯤 됐는데, 수면 문제도 그 무렵에 같이 시작된 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014); 적응장애 (D020) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 수면 문제가 집에서 다툼이 늘어난 것과 비슷한 시기에 시작됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 네, 저한테는 그렇게 느껴졌어요. 집에서 다툼이 심해질 때쯤 잠도 나빠졌어요. 그 다툼들을 계속 되새기고, 일 문제도 마찬가지였고, 그러다 새벽 3~4시쯤 되면 제대로 못 잔 느낌으로 깨어 있었어요. 그게 직원 지원 프로그램에 전화하게 만든 이유예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014); 적응장애 (D020) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 직장에서 특별히 수면 문제에 영향을 주고 있다고 생각하시는 일이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네, 일도 확실히 그 일부예요. 침대에 누워서 그날 있었던 일들, 처리해야 할 일들이나 잘 안 풀린 대화들을 되새기게 되고, 그게 집에서의 다툼이랑 섞이게 돼요. 결국 새벽 3~4시쯤 깨서 전혀 쉰 적이 없는 느낌이 들어요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014); 적응장애 (D020) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 집에서의 다툼이랑 업무 스트레스가 해결되면 수면 문제가 나아질 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 네, 적어도 어느 정도는 나아질 것 같아요. 대부분은 제가 누워서 일 문제랑 집에서의 다툼을 되새기는 거예요. 그러다 새벽 3~4시쯤 깨서 제대로 잔 적이 없는 느낌으로 하루를 시작해요. 그게 결국 심해져서 직원 지원 프로그램에 전화하게 된 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014); 적응장애 (D020) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 수면 문제를 유발한 특정한 사건이나 상황이 있었다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 딱 하나의 사건이 있었는지는 잘 모르겠어요. 그보다는 업무 스트레스랑 집에서의 다툼이 쌓이기 시작했고, 그러다 밤이 되면 그걸 다 되새기게 됐어요. 새벽 3~4시쯤 깨서 제대로 못 잔 느낌이 들었고요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014); 적응장애 (D020) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 주요우울장애 (D013)
 인구통계: 성별 남성 / 나이 37 / 직업상태 sales manager / 최종학력 학사
@@ -575,488 +999,39 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S027
-배경 서술: 케빈의 우울 삽화는 그의 늦은 밤 업무 몰입, 주말 테일게이트 파티, 씀씀이, 그리고 가정에 쏟을 에너지가 부족한 것에 대해 배우자와의 다툼이 급격히 늘어나면서 시작되었다. 1년 2개월에 걸쳐 이 갈등만으로는 변화를 완전히 설명할 수 없었지만, 이는 그가 농구, 볼링, 음악 페스티벌, 바비큐 모임, 그리고 한때 그를 활력 넘치게 했던 영업 코칭에까지 점차 흥미를 잃어가는 배경이 되었다. 그의 식욕, 수면, 업무 속도, 자신감, 의사결정 능력 모두 눈에 띄게 변하면서 예측치가 미끄러졌고, 그는 죄책감과 무가치감, 그리고 가족이 자신 없이 더 나을지도 모른다는 반복적인 생각에 사로잡히게 되었지만, 여전히 기능 수준이 떨어진 채로나마 생활은 이어갔다. 반복적으로 시도해봐도 중요한 고객 프레젠테이션을 더 이상 준비할 수 없다는 것을 깨달은 후, 그는 회사의 직원 지원 프로그램을 통해 스스로 정신과 진료 의뢰를 요청했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제일 큰 문제는 잠인 것 같아요. 직원 지원 프로그램에 결국 전화한 건 요즘 잠을 거의 제대로 못 자서예요. 누워 있으면 일 문제랑 집에서 있었던 다툼들을 계속 되새기게 되고, 그러다 새벽 3~4시쯤 깨요. 하루를 시작할 때쯤이면 제대로 쉰 적이 없는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 일상적인 일들에 대해 지나치게 걱정하시는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 이것저것 생각을 하긴 하는데, 그게 지나친 걱정인지는 모르겠어요. 그냥 가끔 머릿속에 뭔가가 걸려서 안 빠지는 느낌에 더 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 낮 동안 피곤하거나 지친 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 그래요. 대부분의 날에는 꽤 지친 상태로, 이미 진 빠진 채로 하루를 시작하는 느낌이에요. 새벽 3~4시쯤 깨서 제대로 다시 잠들지 못하니까, 실제로 쉰 적이 없는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 최근에 공황 발작을 경험하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 갑자기 숨을 못 쉬겠다거나 통제력을 잃는 것 같은 느낌은 없었어요. 적어도 제가 공황 발작이라고 부를 만한 건 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 수면 부족 때문에 직장이나 집에서 집중하거나 초점을 맞추는 데 어려움을 겪고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 확실히요. 특히 직장에서요. 예전엔 영업 예측이나 고객 프레젠테이션을 꽤 빨리 끝냈는데, 지금은 같은 슬라이드를 계속 읽고, 숫자를 다시 의심하고, 그래도 뭘 말하려는 건지 계속 막혀 있는 느낌이에요. 답답해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 직장이나 집에서 수면 문제에 영향을 주고 있을 만한 특별히 스트레스 받는 일이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 주로 일 문제랑 집에서의 다툼들이에요. 침대에 누우면 하루를 되짚어보게 돼요 — 해야 할 일, 망친 일, 잘 안 풀렸던 대화들 같은 거요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유예요, 잠을 제대로 못 자니까요. 새벽 3~4시쯤 깨고 나면 하루가 제대로 쉰 적이 없는 느낌으로 시작돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 항상 같은 시간에 깨는 것처럼, 깨는 시간에 어떤 패턴이나 규칙성을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네, 꽤 규칙적이에요. 보통 새벽 3~4시쯤 깨고, 그냥 깨어 있으면서 일이나 집에서의 다툼에 대해 생각하게 돼요. 그러고 나면 한참 침대에 있었어도 실제로 쉬었다는 느낌이 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 반복되는 악몽이나 불쾌한 꿈을 꾸시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 악몽까지는 아니에요. 그보다는 계속 잠들어 있지를 못하는 거예요 — 누워서 일 문제나 집에서의 다툼을 계속 되새기다가, 새벽 3~4시쯤 깨서 그냥 제대로 쉰 적이 없는 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 한밤중에 깨기 직전에 특별히 생각하거나 걱정하는 게 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네, 보통은 일이거나 집에서 다투다가 제가 한 말 같은 거예요. 반쯤 깨어 있는 상태에서 이미 그걸 되새기고 있어요 — 뭘 망쳤는지, 앞으로 뭘 처리해야 하는지 — 그러다 새벽 3~4시쯤 완전히 깨요. 그 이후에는 잤다는 느낌이 별로 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 밤 초반에 잠드는 데 어려움을 겪으시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네, 어떤 날은 그래요. 침대에 누워서 그냥 일 문제나 집에서의 다툼을 계속 되새기게 돼요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유 중 하나예요 — 잠을 제대로 못 자고, 잠들어도 새벽 3~4시쯤 깨서 하루를 제대로 못 쉰 느낌으로 시작해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 잠들기 직전에 일어나는 일이나 생각하는 게 몇 시간 후에 깨는 것과 관련이 있을 만한 게 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네, 주로 누워서 일 문제나 집에서의 다툼을 되새기고 있는 것 같아요. 무슨 일이 있었는지, 뭘 처리해야 하는지 계속 되풀이하다가, 결국 새벽 3~4시쯤 깨게 돼요. 그게 정말 직원 지원 프로그램에 전화하게 만든 이유예요 — 그냥 잠을 제대로 못 자고, 전혀 쉰 적이 없는 느낌으로 하루를 시작해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 직장이나 집에서 특별히 가장 스트레스를 많이 주고 수면 문제에 영향을 주는 한 가지가 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 딱 한 가지는 아니에요, 정말로요. 업무 스트레스랑 집에서의 다툼이 합쳐진 거예요. 침대에 누워서 그걸 다 되새기기 시작하고, 잠이 들어도 새벽 3~4시쯤 깨요. 그게 결국 직원 지원 프로그램에 전화하게 만든 거예요 — 잠을 거의 못 자고 전혀 쉬지 못한 느낌으로 하루를 시작해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 침대에 누워서 잠을 못 잘 때 불안하거나 초조한 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 불안이라고 딱 말할 수 있을지는 모르겠어요. 확실히 긴장돼 있고 머릿속이 바쁘긴 한데, 그게 불안인지 아니면 그냥... 생각을 끌 수가 없는 건지 제대로 신경 써서 본 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 직장 스트레스나 집에서의 다툼이 항상 머릿속에 있나요, 아니면 그런 생각들을 잠시 밀어둘 수 있는 때도 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 낮에는 밀어둘 수 있는 시간이 있어요, 특히 바쁠 때는요. 근데 밤이 되면 다시 돌아와요. 침대에 누우면 일 문제나 집에서의 다툼을 다시 되새기게 되고, 그러다 새벽 3~4시쯤 깨서 제대로 잔 적이 없는 느낌이 들어요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 지금 상태 때문에 사회적 관계나 여가 활동에 어려움을 겪고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 네, 그런 것 같아요. 예전엔 픽업 농구, 볼링 나이트, 음악 페스티벌, 아니면 친구들 불러서 훈제기 돌리는 것 같은 걸 정말 기대했거든요. 요즘엔 취소하거나, 가더라도 그냥 거기 있기만 해요... 즐기기보다는 그냥 하는 척만 하는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 수면 문제가 시작된 것과 비슷한 시기에 시작된 특별한 일이 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 네. 집에서의 다툼이 훨씬 심해졌을 때 시작된 것 같아요. 그게... 이제 한 1년 2개월쯤 됐는데, 수면 문제도 그 무렵에 같이 시작된 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014); 적응장애 (D020) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 수면 문제가 집에서 다툼이 늘어난 것과 비슷한 시기에 시작됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 네, 저한테는 그렇게 느껴졌어요. 집에서 다툼이 심해질 때쯤 잠도 나빠졌어요. 그 다툼들을 계속 되새기고, 일 문제도 마찬가지였고, 그러다 새벽 3~4시쯤 되면 제대로 못 잔 느낌으로 깨어 있었어요. 그게 직원 지원 프로그램에 전화하게 만든 이유예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014); 적응장애 (D020) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 직장에서 특별히 수면 문제에 영향을 주고 있다고 생각하시는 일이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네, 일도 확실히 그 일부예요. 침대에 누워서 그날 있었던 일들, 처리해야 할 일들이나 잘 안 풀린 대화들을 되새기게 되고, 그게 집에서의 다툼이랑 섞이게 돼요. 결국 새벽 3~4시쯤 깨서 전혀 쉰 적이 없는 느낌이 들어요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014); 적응장애 (D020) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 집에서의 다툼이랑 업무 스트레스가 해결되면 수면 문제가 나아질 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 네, 적어도 어느 정도는 나아질 것 같아요. 대부분은 제가 누워서 일 문제랑 집에서의 다툼을 되새기는 거예요. 그러다 새벽 3~4시쯤 깨서 제대로 잔 적이 없는 느낌으로 하루를 시작해요. 그게 결국 심해져서 직원 지원 프로그램에 전화하게 된 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014); 적응장애 (D020) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 수면 문제를 유발한 특정한 사건이나 상황이 있었다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 딱 하나의 사건이 있었는지는 잘 모르겠어요. 그보다는 업무 스트레스랑 집에서의 다툼이 쌓이기 시작했고, 그러다 밤이 되면 그걸 다 되새기게 됐어요. 새벽 3~4시쯤 깨서 제대로 못 잔 느낌이 들었고요. 그게 결국 직원 지원 프로그램에 전화하게 만든 이유예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 케빈의 우울 삽화는 그의 늦은 밤 업무 몰입, 주말 테일게이트 파티, 씀씀이, 그리고 가정에 쏟을 에너지가 부족한 것에 대해 배우자와의 다툼이 급격히 늘어나면서 시작되었다. 1년 2개월에 걸쳐 이 갈등만으로는 변화를 완전히 설명할 수 없었지만, 이는 그가 농구, 볼링, 음악 페스티벌, 바비큐 모임, 그리고 한때 그를 활력 넘치게 했던 영업 코칭에까지 점차 흥미를 잃어가는 배경이 되었다. 그의 식욕, 수면, 업무 속도, 자신감, 의사결정 능력 모두 눈에 띄게 변하면서 예측치가 미끄러졌고, 그는 죄책감과 무가치감, 그리고 가족이 자신 없이 더 나을지도 모른다는 반복적인 생각에 사로잡히게 되었지만, 여전히 기능 수준이 떨어진 채로나마 생활은 이어갔다. 반복적으로 시도해봐도 중요한 고객 프레젠테이션을 더 이상 준비할 수 없다는 것을 깨달은 후, 그는 회사의 직원 지원 프로그램을 통해 스스로 정신과 진료 의뢰를 요청했다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014); 적응장애 (D020) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: F51.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+          <t>의사의 최종 진단: None (None, ICD: F51.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D013_S001_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S001_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1027,11 +1032,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D013_S001_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S001_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.089</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.089</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3523</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
